--- a/AAII_Financials/Yearly/BSY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BSY_YR_FIN.xlsx
@@ -1077,25 +1077,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1131900</v>
+        <v>1117500</v>
       </c>
       <c r="E17" s="3">
-        <v>1039900</v>
+        <v>1027500</v>
       </c>
       <c r="F17" s="3">
-        <v>967400</v>
+        <v>953800</v>
       </c>
       <c r="G17" s="3">
-        <v>865100</v>
+        <v>880900</v>
       </c>
       <c r="H17" s="3">
-        <v>850000</v>
+        <v>754900</v>
       </c>
       <c r="I17" s="3">
-        <v>618300</v>
+        <v>618200</v>
       </c>
       <c r="J17" s="3">
-        <v>590300</v>
+        <v>589900</v>
       </c>
       <c r="K17" s="3">
         <v>557100</v>
@@ -1122,25 +1122,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>369900</v>
+        <v>384300</v>
       </c>
       <c r="E18" s="3">
-        <v>313200</v>
+        <v>325600</v>
       </c>
       <c r="F18" s="3">
-        <v>261000</v>
+        <v>274600</v>
       </c>
       <c r="G18" s="3">
-        <v>234000</v>
+        <v>218200</v>
       </c>
       <c r="H18" s="3">
-        <v>115100</v>
+        <v>210100</v>
       </c>
       <c r="I18" s="3">
-        <v>183200</v>
+        <v>183400</v>
       </c>
       <c r="J18" s="3">
-        <v>146300</v>
+        <v>146700</v>
       </c>
       <c r="K18" s="3">
         <v>134600</v>
@@ -1186,25 +1186,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-3400</v>
+        <v>11000</v>
       </c>
       <c r="E20" s="3">
-        <v>-3700</v>
+        <v>8600</v>
       </c>
       <c r="F20" s="3">
-        <v>13300</v>
+        <v>26900</v>
       </c>
       <c r="G20" s="3">
-        <v>10400</v>
+        <v>-5400</v>
       </c>
       <c r="H20" s="3">
-        <v>1600</v>
+        <v>96600</v>
       </c>
       <c r="I20" s="3">
-        <v>-20800</v>
+        <v>-20600</v>
       </c>
       <c r="J20" s="3">
-        <v>6800</v>
+        <v>7200</v>
       </c>
       <c r="K20" s="3">
         <v>200</v>
@@ -1726,25 +1726,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>3400</v>
+        <v>-11000</v>
       </c>
       <c r="E32" s="3">
-        <v>3700</v>
+        <v>-8600</v>
       </c>
       <c r="F32" s="3">
-        <v>-13300</v>
+        <v>-26900</v>
       </c>
       <c r="G32" s="3">
-        <v>-10400</v>
+        <v>5400</v>
       </c>
       <c r="H32" s="3">
-        <v>-1600</v>
+        <v>-96600</v>
       </c>
       <c r="I32" s="3">
-        <v>20800</v>
+        <v>20600</v>
       </c>
       <c r="J32" s="3">
-        <v>-6800</v>
+        <v>-7200</v>
       </c>
       <c r="K32" s="3">
         <v>-200</v>
